--- a/tools/project_gantt.xlsx
+++ b/tools/project_gantt.xlsx
@@ -2741,7 +2741,7 @@
       <formula1>"Yes";"Yes";"No"</formula1>
     </dataValidation>
     <dataValidation sqref="B30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"Weekly,Monthly"</formula1>
+      <formula1>"Weekly;Monthly"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
